--- a/sim_proj_updated/paretotable.xlsx
+++ b/sim_proj_updated/paretotable.xlsx
@@ -30,61 +30,61 @@
     <t>Cumulative Percentage</t>
   </si>
   <si>
-    <t>polluted_Ca</t>
-  </si>
-  <si>
-    <t>polluted_Mg</t>
-  </si>
-  <si>
-    <t>polluted_TH</t>
-  </si>
-  <si>
-    <t>polluted_K</t>
-  </si>
-  <si>
-    <t>polluted_Na</t>
-  </si>
-  <si>
-    <t>polluted_SO4</t>
-  </si>
-  <si>
-    <t>polluted_Cl</t>
-  </si>
-  <si>
-    <t>polluted_TDS</t>
-  </si>
-  <si>
-    <t>polluted_EC</t>
-  </si>
-  <si>
-    <t>polluted_TUR</t>
-  </si>
-  <si>
-    <t>polluted_TPC</t>
-  </si>
-  <si>
-    <t>polluted_coliform</t>
-  </si>
-  <si>
-    <t>polluted_Ecoli</t>
-  </si>
-  <si>
-    <t>polluted_ALK</t>
-  </si>
-  <si>
-    <t>polluted_temp</t>
-  </si>
-  <si>
-    <t>polluted_ph</t>
-  </si>
-  <si>
-    <t>polluted_Do</t>
-  </si>
-  <si>
-    <t>polluted_PO4</t>
-  </si>
-  <si>
-    <t>polluted_NO3</t>
+    <t>Ca</t>
+  </si>
+  <si>
+    <t>Mg</t>
+  </si>
+  <si>
+    <t>TH</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>Na</t>
+  </si>
+  <si>
+    <t>SO4</t>
+  </si>
+  <si>
+    <t>Cl</t>
+  </si>
+  <si>
+    <t>TDS</t>
+  </si>
+  <si>
+    <t>EC</t>
+  </si>
+  <si>
+    <t>TUR</t>
+  </si>
+  <si>
+    <t>TPC</t>
+  </si>
+  <si>
+    <t>Coliform</t>
+  </si>
+  <si>
+    <t>E. coli</t>
+  </si>
+  <si>
+    <t>ALK</t>
+  </si>
+  <si>
+    <t>Temperature</t>
+  </si>
+  <si>
+    <t>pH</t>
+  </si>
+  <si>
+    <t>DO</t>
+  </si>
+  <si>
+    <t>PO4</t>
+  </si>
+  <si>
+    <t>NO3</t>
   </si>
 </sst>
 </file>
